--- a/Assets/Excel/Buff配置表.xlsx
+++ b/Assets/Excel/Buff配置表.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\TurnDemo\Assets\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="51">
   <si>
     <t>f_id</t>
   </si>
@@ -57,6 +62,9 @@
   </si>
   <si>
     <t>f_layerVariationType</t>
+  </si>
+  <si>
+    <t>f_statusState</t>
   </si>
   <si>
     <t>int</t>
@@ -111,7 +119,13 @@
   <si>
     <t>状态层数变化类型
 0：降低层数
-1：移除所有</t>
+1：移除所有(回合主导)</t>
+  </si>
+  <si>
+    <t>状态何时开始结算
+0：立刻结算，回合结束时会结算；
+1：下一回合结算，当前回合结束时不会结算；
+仅使用于：本次回合已经结束之前才创建的，而且它应该作用于下一轮正常回合。非这种情况默认为0</t>
   </si>
   <si>
     <t>庇佑</t>
@@ -1162,7 +1176,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.45" customWidth="1"/>
@@ -1174,9 +1188,10 @@
     <col min="8" max="8" width="17.125" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
     <col min="10" max="10" width="22.625" customWidth="1"/>
+    <col min="11" max="11" width="24.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="33" customHeight="1" spans="1:10">
+    <row r="1" s="1" customFormat="1" ht="33" customHeight="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1207,85 +1222,94 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="22" customHeight="1" spans="1:10">
+    <row r="2" s="1" customFormat="1" ht="22" customHeight="1" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="22" customHeight="1" spans="1:10">
+    <row r="3" s="1" customFormat="1" ht="22" customHeight="1" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="100" customHeight="1" spans="1:10">
+    <row r="4" s="1" customFormat="1" ht="135" spans="1:11">
       <c r="A4" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" ht="48" customHeight="1" spans="1:10">
+    <row r="5" s="2" customFormat="1" ht="48" customHeight="1" spans="1:11">
       <c r="A5" s="2">
         <v>101</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D5" s="2">
         <v>0</v>
@@ -1308,16 +1332,19 @@
       <c r="J5" s="2">
         <v>1</v>
       </c>
+      <c r="K5" s="6">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" s="2" customFormat="1" ht="48" customHeight="1" spans="1:10">
+    <row r="6" s="2" customFormat="1" ht="48" customHeight="1" spans="1:11">
       <c r="A6" s="2">
         <v>111</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
@@ -1340,16 +1367,19 @@
       <c r="J6" s="2">
         <v>1</v>
       </c>
+      <c r="K6" s="2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" s="2" customFormat="1" ht="48" customHeight="1" spans="1:10">
+    <row r="7" s="2" customFormat="1" ht="48" customHeight="1" spans="1:11">
       <c r="A7" s="2">
         <v>121</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
@@ -1372,16 +1402,19 @@
       <c r="J7" s="2">
         <v>1</v>
       </c>
+      <c r="K7" s="2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" s="3" customFormat="1" ht="38" customHeight="1" spans="1:10">
+    <row r="8" s="3" customFormat="1" ht="38" customHeight="1" spans="1:11">
       <c r="A8" s="3">
         <v>201</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D8" s="3">
         <v>0</v>
@@ -1404,16 +1437,19 @@
       <c r="J8" s="3">
         <v>1</v>
       </c>
+      <c r="K8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" s="3" customFormat="1" ht="38" customHeight="1" spans="1:10">
+    <row r="9" s="3" customFormat="1" ht="38" customHeight="1" spans="1:11">
       <c r="A9" s="3">
         <v>211</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D9" s="3">
         <v>0</v>
@@ -1436,16 +1472,19 @@
       <c r="J9" s="3">
         <v>1</v>
       </c>
+      <c r="K9" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" s="3" customFormat="1" ht="38" customHeight="1" spans="1:10">
+    <row r="10" s="3" customFormat="1" ht="38" customHeight="1" spans="1:11">
       <c r="A10" s="3">
         <v>221</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D10" s="3">
         <v>0</v>
@@ -1468,16 +1507,19 @@
       <c r="J10" s="3">
         <v>1</v>
       </c>
+      <c r="K10" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" s="2" customFormat="1" ht="49" customHeight="1" spans="1:10">
+    <row r="11" s="2" customFormat="1" ht="49" customHeight="1" spans="1:11">
       <c r="A11" s="2">
         <v>301</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D11" s="2">
         <v>0</v>
@@ -1498,18 +1540,21 @@
         <v>1</v>
       </c>
       <c r="J11" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K11" s="2">
+        <v>1</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" ht="49" customHeight="1" spans="1:10">
+    <row r="12" s="2" customFormat="1" ht="49" customHeight="1" spans="1:11">
       <c r="A12" s="2">
         <v>311</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
@@ -1521,7 +1566,7 @@
         <v>1</v>
       </c>
       <c r="G12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" s="2">
         <v>2</v>
@@ -1530,18 +1575,21 @@
         <v>1</v>
       </c>
       <c r="J12" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K12" s="2">
+        <v>1</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" ht="49" customHeight="1" spans="1:10">
+    <row r="13" s="2" customFormat="1" ht="49" customHeight="1" spans="1:11">
       <c r="A13" s="2">
         <v>321</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
@@ -1553,27 +1601,30 @@
         <v>1</v>
       </c>
       <c r="G13" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H13" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I13" s="2">
         <v>1</v>
       </c>
       <c r="J13" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K13" s="2">
+        <v>1</v>
       </c>
     </row>
-    <row r="14" s="4" customFormat="1" ht="49" customHeight="1" spans="1:10">
+    <row r="14" s="4" customFormat="1" ht="49" customHeight="1" spans="1:11">
       <c r="A14" s="4">
         <v>1011</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D14" s="4">
         <v>2</v>
@@ -1596,16 +1647,19 @@
       <c r="J14" s="4">
         <v>0</v>
       </c>
+      <c r="K14" s="4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" s="4" customFormat="1" ht="49" customHeight="1" spans="1:10">
+    <row r="15" s="4" customFormat="1" ht="49" customHeight="1" spans="1:11">
       <c r="A15" s="4">
         <v>1021</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D15" s="4">
         <v>5</v>
@@ -1628,16 +1682,19 @@
       <c r="J15" s="4">
         <v>0</v>
       </c>
+      <c r="K15" s="4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" s="4" customFormat="1" ht="49" customHeight="1" spans="1:10">
+    <row r="16" s="4" customFormat="1" ht="49" customHeight="1" spans="1:11">
       <c r="A16" s="4">
         <v>1041</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D16" s="4">
         <v>1</v>
@@ -1660,16 +1717,19 @@
       <c r="J16" s="4">
         <v>0</v>
       </c>
+      <c r="K16" s="4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" s="4" customFormat="1" ht="49" customHeight="1" spans="1:10">
+    <row r="17" s="4" customFormat="1" ht="49" customHeight="1" spans="1:11">
       <c r="A17" s="4">
         <v>1051</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D17" s="4">
         <v>0</v>
@@ -1684,13 +1744,16 @@
         <v>1</v>
       </c>
       <c r="H17" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I17" s="4">
         <v>3</v>
       </c>
       <c r="J17" s="4">
         <v>1</v>
+      </c>
+      <c r="K17" s="4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
